--- a/skills/it-revisione/assets/investment-policy-statement.xlsx
+++ b/skills/it-revisione/assets/investment-policy-statement.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -571,34 +571,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -744,7 +744,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
@@ -1032,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="17" t="str">
-        <f aca="false">IF(ABS(B25-1)&lt;0.001,"✓ somma 100%","⚠ deve fare 100% (ora "&amp;TEXT(B25,"0.0%")&amp;")")</f>
+        <f aca="false">IF(ABS(B25-1)&lt;0.001,"✓ somma 100%","⚠ deve fare 100% (ora "&amp;FIXED((B25)*100,1)&amp;"%"&amp;")")</f>
         <v>✓ somma 100%</v>
       </c>
       <c r="D25" s="17"/>

--- a/skills/it-revisione/assets/investment-policy-statement.xlsx
+++ b/skills/it-revisione/assets/investment-policy-statement.xlsx
@@ -214,7 +214,7 @@
     <t xml:space="preserve">•  Usare le minus in scadenza entro il 31/12.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Versare al fondo pensione entro il 31/12 per la deduzione.</t>
+    <t xml:space="preserve">•  Versare al fondo pensione entro il 31/12 per la deduzione; comunicare al fondo i contributi non dedotti dell'anno precedente.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Preferire strumenti compensabili quando c'è zainetto.</t>
@@ -238,7 +238,7 @@
     <t xml:space="preserve">novembre-dicembre</t>
   </si>
   <si>
-    <t xml:space="preserve">per le scadenze minus e il versamento al fondo pensione</t>
+    <t xml:space="preserve">per le scadenze minus, il versamento al fondo pensione e la comunicazione dei non dedotti</t>
   </si>
   <si>
     <t xml:space="preserve">Regola: modifico questo IPS solo per eventi STRUTTURALI (nuovo obiettivo, cambio di reddito o fase di vita), mai in reazione a un movimento di mercato.</t>
